--- a/artfynd/A 39618-2026 artfynd.xlsx
+++ b/artfynd/A 39618-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -788,9 +788,131 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>136857955</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5485</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Riddarhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>527625</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6629918</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136857955</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39618-2026 artfynd.xlsx
+++ b/artfynd/A 39618-2026 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>136857955</v>
       </c>
       <c r="B3" t="n">
-        <v>5485</v>
+        <v>5491</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
